--- a/csv/videos.xlsx
+++ b/csv/videos.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alex\Documents\GitHub\ro-av-deepfake-dataset\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alex\Documents\GitHub\ro-av-deepfake-dataset\csv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00346E96-E51C-48AC-8D2E-1C1BDAD172FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8FBA634-DFAE-40E0-A42A-39AE2053517D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15930" yWindow="3855" windowWidth="21600" windowHeight="11385" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Muntenia" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1200" uniqueCount="543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1526" uniqueCount="546">
   <si>
     <t>https://www.youtube.com/watch?v=l2I7D1HsJmw</t>
   </si>
@@ -279,69 +279,39 @@
     <t>https://www.youtube.com/watch?v=3f4DnN1Pxjw</t>
   </si>
   <si>
-    <t>https://youtu.be/FAPEdnmr63w?si=TuYsIk0JLveimJF0</t>
-  </si>
-  <si>
     <t>1:00-20:00</t>
   </si>
   <si>
-    <t>https://youtu.be/o5i9cc7oe38?si=zoSC2KRIsQIcyoYs</t>
-  </si>
-  <si>
     <t>1:30-7:00</t>
   </si>
   <si>
     <t>1:00-7:00</t>
   </si>
   <si>
-    <t>https://youtu.be/R4ch3Cu8FJA?si=Y6m8r7ZRU9OL2AAl</t>
-  </si>
-  <si>
     <t>12:00-17:00</t>
   </si>
   <si>
-    <t>https://youtu.be/sQ3QrGvK03E?si=Cd50wgeRKPXsn5tv</t>
-  </si>
-  <si>
     <t>9:30-15:00</t>
   </si>
   <si>
-    <t>https://youtu.be/KT1NWjLSDLU?si=02x2CG_BZOb83VjZ</t>
-  </si>
-  <si>
     <t>2:40-8:50</t>
   </si>
   <si>
     <t>Total</t>
   </si>
   <si>
-    <t>https://youtu.be/frBTWyXiPF0?si=8q3mJSCO2wK6S36w</t>
-  </si>
-  <si>
     <t>3:00-8:00</t>
   </si>
   <si>
-    <t>https://youtu.be/I6j09Iys4Xo?si=iUh2OJN87dM9GT2D</t>
-  </si>
-  <si>
     <t>2:35-6:40</t>
   </si>
   <si>
-    <t>https://youtu.be/F_Cnppr3hFc?si=rNcuFNIkHlE3AG2V</t>
-  </si>
-  <si>
     <t>5:42-10:00</t>
   </si>
   <si>
-    <t>https://youtu.be/2WUMgEA8zCM?si=JAxiTghKgk6q7h53</t>
-  </si>
-  <si>
     <t>2:30-6:55</t>
   </si>
   <si>
-    <t>https://youtu.be/_3OLJk5a0dU?si=hQGk59eHV1BySqUI</t>
-  </si>
-  <si>
     <t>1:40-6:50</t>
   </si>
   <si>
@@ -1509,9 +1479,6 @@
     <t>0:00-9:29</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=QdTq_r1UP8E</t>
-  </si>
-  <si>
     <t>5:55-13:04</t>
   </si>
   <si>
@@ -1669,6 +1636,48 @@
   </si>
   <si>
     <t>2:19-7:31</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=QdTq_R1up8e</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=frBTWyXiPF0</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=_3OLJk5a0dU</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=FAPEdnmr63w</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=o5i9cc7oe38</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=R4ch3Cu8FJA</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=sQ3QrGvK03E</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=KT1NWjLSDLU</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=I6j09Iys4Xo</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=F_Cnppr3hFc</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=2WUMgEA8zCM</t>
   </si>
 </sst>
 </file>
@@ -1748,7 +1757,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1769,28 +1778,57 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="2" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Output" xfId="2" builtinId="21"/>
   </cellStyles>
-  <dxfs count="34">
+  <dxfs count="39">
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFCBF9CD"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFCBF9CD"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor auto="1"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFCBF9CD"/>
+        </patternFill>
+      </fill>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color rgb="FF7F7F7F"/>
-        </top>
-      </border>
     </dxf>
     <dxf>
       <fill>
@@ -2030,6 +2068,22 @@
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color rgb="FF7F7F7F"/>
+        </top>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -2051,85 +2105,90 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1F374B77-EF7F-49D3-95ED-543F09538973}" name="Table2" displayName="Table2" ref="A1:E96" totalsRowShown="0" tableBorderDxfId="3" headerRowCellStyle="Output">
-  <autoFilter ref="A1:E96" xr:uid="{1F374B77-EF7F-49D3-95ED-543F09538973}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{1F374B77-EF7F-49D3-95ED-543F09538973}" name="Table2" displayName="Table2" ref="A1:F96" totalsRowShown="0" tableBorderDxfId="38" headerRowCellStyle="Output">
+  <autoFilter ref="A1:F96" xr:uid="{1F374B77-EF7F-49D3-95ED-543F09538973}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E96">
     <sortCondition descending="1" ref="D1:D96"/>
   </sortState>
-  <tableColumns count="5">
+  <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{A8E13BAF-A9FB-4F50-A915-7E9282EE7C8D}" name="Link" dataCellStyle="Hyperlink"/>
-    <tableColumn id="2" xr3:uid="{16D12566-EC51-47B0-8BE9-AA1A55D15053}" name="Speakers" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{16D12566-EC51-47B0-8BE9-AA1A55D15053}" name="Speakers" dataDxfId="37"/>
     <tableColumn id="3" xr3:uid="{A4D262DF-0A4A-4BB8-A9B7-B2F1E4A5A9B2}" name="City"/>
-    <tableColumn id="4" xr3:uid="{3F6CD110-BFE3-400E-9A5B-0D5F88861464}" name="Category" dataDxfId="1"/>
-    <tableColumn id="5" xr3:uid="{C00352FE-678F-4E83-BC8A-73573F531AE3}" name="Trim" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{3F6CD110-BFE3-400E-9A5B-0D5F88861464}" name="Category" dataDxfId="36"/>
+    <tableColumn id="5" xr3:uid="{C00352FE-678F-4E83-BC8A-73573F531AE3}" name="Trim" dataDxfId="35"/>
+    <tableColumn id="6" xr3:uid="{362F7C54-50EF-44F4-8936-B4DCC114F633}" name="Gender" dataDxfId="3"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1E259DE3-4B37-4150-B909-CDDBF56EAAC8}" name="Table1" displayName="Table1" ref="A1:E88" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32" tableBorderDxfId="31" headerRowCellStyle="Output">
-  <autoFilter ref="A1:E88" xr:uid="{1E259DE3-4B37-4150-B909-CDDBF56EAAC8}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1E259DE3-4B37-4150-B909-CDDBF56EAAC8}" name="Table1" displayName="Table1" ref="A1:F88" totalsRowShown="0" headerRowDxfId="34" dataDxfId="33" tableBorderDxfId="32" headerRowCellStyle="Output">
+  <autoFilter ref="A1:F88" xr:uid="{1E259DE3-4B37-4150-B909-CDDBF56EAAC8}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E87">
     <sortCondition descending="1" ref="D1:D87"/>
   </sortState>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{62084203-1A8A-4077-A6C6-B157FA48A7FA}" name="Link" dataDxfId="30"/>
-    <tableColumn id="2" xr3:uid="{F21E8710-1ACB-4866-9E39-E503A6A8B8F2}" name="Speakers" dataDxfId="29"/>
-    <tableColumn id="3" xr3:uid="{CE1B8206-482B-4F8F-9910-BF48CA1F665C}" name="City" dataDxfId="28"/>
-    <tableColumn id="4" xr3:uid="{834028F5-C678-4FD7-98C8-9F0159A944C0}" name="Category" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{F5D08F42-F8A6-443D-AEE0-DDF4C75B3A70}" name="Trim" dataDxfId="26"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{62084203-1A8A-4077-A6C6-B157FA48A7FA}" name="Link" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{F21E8710-1ACB-4866-9E39-E503A6A8B8F2}" name="Speakers" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{CE1B8206-482B-4F8F-9910-BF48CA1F665C}" name="City" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{834028F5-C678-4FD7-98C8-9F0159A944C0}" name="Category" dataDxfId="28"/>
+    <tableColumn id="5" xr3:uid="{F5D08F42-F8A6-443D-AEE0-DDF4C75B3A70}" name="Trim" dataDxfId="27"/>
+    <tableColumn id="6" xr3:uid="{93B93209-489A-4AD7-B56C-3A4EFC28EFBA}" name="Gender" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5FB8BC92-48E7-4C5E-8055-292233253902}" name="Table5" displayName="Table5" ref="A1:E85" totalsRowShown="0" headerRowDxfId="25" dataDxfId="24" tableBorderDxfId="23" headerRowCellStyle="Output">
-  <autoFilter ref="A1:E85" xr:uid="{5FB8BC92-48E7-4C5E-8055-292233253902}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{5FB8BC92-48E7-4C5E-8055-292233253902}" name="Table5" displayName="Table5" ref="A1:F85" totalsRowShown="0" headerRowDxfId="26" dataDxfId="25" tableBorderDxfId="24" headerRowCellStyle="Output">
+  <autoFilter ref="A1:F85" xr:uid="{5FB8BC92-48E7-4C5E-8055-292233253902}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E85">
     <sortCondition descending="1" ref="D1:D85"/>
   </sortState>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{E853F3B6-335F-4CE8-AA32-003A4EFDCCA1}" name="Link" dataDxfId="22"/>
-    <tableColumn id="2" xr3:uid="{7B2A43B2-05FE-4A47-B264-B5E60D92EF45}" name="Speakers" dataDxfId="21"/>
-    <tableColumn id="3" xr3:uid="{EF02EBA4-97A3-4E5F-B0C2-3CE260709B8B}" name="City" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{9F0015D2-ABC1-47BB-88A3-2D7D3198C579}" name="Category" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{DC980E3B-B8B0-4B55-BE5D-F0EF1AC45777}" name="Trim" dataDxfId="18"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{E853F3B6-335F-4CE8-AA32-003A4EFDCCA1}" name="Link" dataDxfId="23"/>
+    <tableColumn id="2" xr3:uid="{7B2A43B2-05FE-4A47-B264-B5E60D92EF45}" name="Speakers" dataDxfId="22"/>
+    <tableColumn id="3" xr3:uid="{EF02EBA4-97A3-4E5F-B0C2-3CE260709B8B}" name="City" dataDxfId="21"/>
+    <tableColumn id="4" xr3:uid="{9F0015D2-ABC1-47BB-88A3-2D7D3198C579}" name="Category" dataDxfId="20"/>
+    <tableColumn id="5" xr3:uid="{DC980E3B-B8B0-4B55-BE5D-F0EF1AC45777}" name="Trim" dataDxfId="19"/>
+    <tableColumn id="6" xr3:uid="{21F4C77E-DF03-4D15-B2F3-D06C988ED227}" name="Gender" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{867C6F45-DE35-4ED4-B445-884AF9F81B4E}" name="Table7" displayName="Table7" ref="A1:E31" totalsRowShown="0" headerRowDxfId="17" dataDxfId="16" tableBorderDxfId="15" headerRowCellStyle="Output">
-  <autoFilter ref="A1:E31" xr:uid="{867C6F45-DE35-4ED4-B445-884AF9F81B4E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{867C6F45-DE35-4ED4-B445-884AF9F81B4E}" name="Table7" displayName="Table7" ref="A1:F31" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17" tableBorderDxfId="16" headerRowCellStyle="Output">
+  <autoFilter ref="A1:F31" xr:uid="{867C6F45-DE35-4ED4-B445-884AF9F81B4E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E31">
     <sortCondition descending="1" ref="D1:D31"/>
   </sortState>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{C00D3581-381B-4E24-8FA9-3A0412866205}" name="Link" dataDxfId="14"/>
-    <tableColumn id="2" xr3:uid="{62DB9036-4083-4F75-A048-9EA165DD5A64}" name="Speakers" dataDxfId="13"/>
-    <tableColumn id="3" xr3:uid="{3C76EA02-B770-4073-928C-466AB48111A2}" name="City" dataDxfId="12"/>
-    <tableColumn id="4" xr3:uid="{CEBD4298-3209-4363-A089-ECA8FB63BACB}" name="Category" dataDxfId="11"/>
-    <tableColumn id="5" xr3:uid="{8A6376B1-8F44-431D-AC79-C262A114FA89}" name="Trim" dataDxfId="10"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{C00D3581-381B-4E24-8FA9-3A0412866205}" name="Link" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{62DB9036-4083-4F75-A048-9EA165DD5A64}" name="Speakers" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{3C76EA02-B770-4073-928C-466AB48111A2}" name="City" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{CEBD4298-3209-4363-A089-ECA8FB63BACB}" name="Category" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{8A6376B1-8F44-431D-AC79-C262A114FA89}" name="Trim" dataDxfId="11"/>
+    <tableColumn id="6" xr3:uid="{A2C53560-CB6C-4322-B4A1-566C98EF1157}" name="Gender" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8229A439-7DCE-423B-9964-E070F8F1CEB4}" name="Table6" displayName="Table6" ref="A1:E35" totalsRowShown="0" dataDxfId="9" headerRowCellStyle="Output">
-  <autoFilter ref="A1:E35" xr:uid="{8229A439-7DCE-423B-9964-E070F8F1CEB4}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{8229A439-7DCE-423B-9964-E070F8F1CEB4}" name="Table6" displayName="Table6" ref="A1:F35" totalsRowShown="0" dataDxfId="10" headerRowCellStyle="Output">
+  <autoFilter ref="A1:F35" xr:uid="{8229A439-7DCE-423B-9964-E070F8F1CEB4}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:E35">
     <sortCondition descending="1" ref="D1:D35"/>
   </sortState>
-  <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{15E119E2-51A8-46E7-9F80-212DA796235F}" name="Link" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{EF27AF91-CCC7-4ED7-85B4-C594FB74E10E}" name="Speakers" dataDxfId="7"/>
-    <tableColumn id="6" xr3:uid="{304A4372-45E6-46FB-9C88-F9B3E1E978A5}" name="City" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{7321F5DA-F457-440C-A02F-A29FA733E0AB}" name="Category" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{9B47429F-65BA-49BA-B055-86DFF92C33EE}" name="Trim" dataDxfId="4"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{15E119E2-51A8-46E7-9F80-212DA796235F}" name="Link" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{EF27AF91-CCC7-4ED7-85B4-C594FB74E10E}" name="Speakers" dataDxfId="8"/>
+    <tableColumn id="6" xr3:uid="{304A4372-45E6-46FB-9C88-F9B3E1E978A5}" name="City" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{7321F5DA-F457-440C-A02F-A29FA733E0AB}" name="Category" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{9B47429F-65BA-49BA-B055-86DFF92C33EE}" name="Trim" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{1CB354B7-E603-4189-8D48-632F645EE555}" name="Gender" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2398,7 +2457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E96"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="57" customWidth="1"/>
@@ -2409,7 +2468,7 @@
     <col min="6" max="6" width="20.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>73</v>
       </c>
@@ -2417,7 +2476,7 @@
         <v>72</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>74</v>
@@ -2425,40 +2484,49 @@
       <c r="E1" s="9" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="9" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="B2" s="5">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="5"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="B3" s="5">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>186</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -2472,10 +2540,13 @@
         <v>4</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>15</v>
       </c>
@@ -2489,8 +2560,11 @@
         <v>4</v>
       </c>
       <c r="E5" s="5"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F5" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>16</v>
       </c>
@@ -2504,8 +2578,11 @@
         <v>4</v>
       </c>
       <c r="E6" s="5"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F6" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>19</v>
       </c>
@@ -2519,8 +2596,11 @@
         <v>4</v>
       </c>
       <c r="E7" s="5"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>31</v>
       </c>
@@ -2534,10 +2614,13 @@
         <v>4</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>531</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>520</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>33</v>
       </c>
@@ -2551,12 +2634,15 @@
         <v>4</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>521</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B10" s="5">
         <v>1</v>
@@ -2568,12 +2654,15 @@
         <v>4</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>522</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B11" s="5">
         <v>1</v>
@@ -2585,12 +2674,15 @@
         <v>4</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>523</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B12" s="5">
         <v>1</v>
@@ -2602,12 +2694,15 @@
         <v>4</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="B13" s="5">
         <v>1</v>
@@ -2619,12 +2714,15 @@
         <v>4</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B14" s="5">
         <v>1</v>
@@ -2636,12 +2734,15 @@
         <v>4</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="B15" s="5">
         <v>1</v>
@@ -2653,12 +2754,15 @@
         <v>4</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="B16" s="5">
         <v>1</v>
@@ -2670,12 +2774,15 @@
         <v>4</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B17" s="5">
         <v>1</v>
@@ -2687,12 +2794,15 @@
         <v>4</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="B18" s="5">
         <v>1</v>
@@ -2704,12 +2814,15 @@
         <v>4</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="B19" s="5">
         <v>1</v>
@@ -2721,12 +2834,15 @@
         <v>4</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="B20" s="5">
         <v>1</v>
@@ -2738,12 +2854,15 @@
         <v>4</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>519</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="B21" s="5">
         <v>1</v>
@@ -2755,12 +2874,15 @@
         <v>4</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+        <v>518</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="B22" s="5">
         <v>1</v>
@@ -2772,12 +2894,15 @@
         <v>4</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>517</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="B23" s="5">
         <v>1</v>
@@ -2789,12 +2914,15 @@
         <v>4</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+        <v>516</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="B24" s="5">
         <v>1</v>
@@ -2806,12 +2934,15 @@
         <v>4</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>515</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="B25" s="5">
         <v>1</v>
@@ -2823,12 +2954,15 @@
         <v>4</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>514</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="B26" s="5">
         <v>1</v>
@@ -2840,12 +2974,15 @@
         <v>4</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="B27" s="5">
         <v>1</v>
@@ -2857,12 +2994,15 @@
         <v>4</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>512</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B28" s="5">
         <v>1</v>
@@ -2876,10 +3016,13 @@
       <c r="E28" s="5" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F28" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="B29" s="5">
         <v>1</v>
@@ -2891,12 +3034,15 @@
         <v>4</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+        <v>234</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="B30" s="5">
         <v>1</v>
@@ -2908,10 +3054,13 @@
         <v>4</v>
       </c>
       <c r="E30" s="5"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F30" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="B31" s="5">
         <v>1</v>
@@ -2923,10 +3072,13 @@
         <v>4</v>
       </c>
       <c r="E31" s="5"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F31" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="B32" s="5">
         <v>1</v>
@@ -2938,10 +3090,13 @@
         <v>4</v>
       </c>
       <c r="E32" s="5"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F32" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="B33" s="5">
         <v>1</v>
@@ -2953,10 +3108,13 @@
         <v>4</v>
       </c>
       <c r="E33" s="5"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F33" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="B34" s="5">
         <v>1</v>
@@ -2968,10 +3126,13 @@
         <v>4</v>
       </c>
       <c r="E34" s="5"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F34" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="B35" s="5">
         <v>1</v>
@@ -2983,10 +3144,13 @@
         <v>4</v>
       </c>
       <c r="E35" s="5"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F35" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="B36" s="5">
         <v>1</v>
@@ -2998,10 +3162,13 @@
         <v>4</v>
       </c>
       <c r="E36" s="5"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F36" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="B37" s="5">
         <v>1</v>
@@ -3013,10 +3180,13 @@
         <v>4</v>
       </c>
       <c r="E37" s="5"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F37" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="B38" s="5">
         <v>1</v>
@@ -3028,12 +3198,15 @@
         <v>4</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+        <v>262</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="B39" s="5">
         <v>1</v>
@@ -3045,12 +3218,15 @@
         <v>4</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="B40" s="5">
         <v>1</v>
@@ -3062,12 +3238,15 @@
         <v>4</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="B41" s="5">
         <v>1</v>
@@ -3079,12 +3258,15 @@
         <v>4</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="B42" s="5">
         <v>1</v>
@@ -3096,12 +3278,15 @@
         <v>4</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="B43" s="5">
         <v>1</v>
@@ -3113,12 +3298,15 @@
         <v>4</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="B44" s="5">
         <v>1</v>
@@ -3130,12 +3318,15 @@
         <v>4</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="B45" s="5">
         <v>1</v>
@@ -3147,12 +3338,15 @@
         <v>4</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+        <v>237</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="B46" s="5">
         <v>1</v>
@@ -3164,12 +3358,15 @@
         <v>4</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+        <v>241</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="B47" s="5">
         <v>1</v>
@@ -3181,12 +3378,15 @@
         <v>4</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="B48" s="5">
         <v>1</v>
@@ -3198,12 +3398,15 @@
         <v>4</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+        <v>247</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="B49" s="5">
         <v>1</v>
@@ -3215,42 +3418,51 @@
         <v>4</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="B50" s="5">
         <v>1</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E50" s="5"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F50" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="B51" s="5">
         <v>1</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D51" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+        <v>264</v>
+      </c>
+      <c r="F51" s="7" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>67</v>
       </c>
@@ -3264,8 +3476,11 @@
         <v>4</v>
       </c>
       <c r="E52" s="5"/>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F52" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>32</v>
       </c>
@@ -3279,12 +3494,15 @@
         <v>4</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+        <v>511</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="B54" s="5">
         <v>1</v>
@@ -3296,25 +3514,31 @@
         <v>4</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B55" s="5">
         <v>1</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E55" s="5"/>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F55" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>34</v>
       </c>
@@ -3328,8 +3552,11 @@
         <v>2</v>
       </c>
       <c r="E56" s="5"/>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F56" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>35</v>
       </c>
@@ -3343,8 +3570,11 @@
         <v>2</v>
       </c>
       <c r="E57" s="5"/>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F57" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
         <v>36</v>
       </c>
@@ -3358,8 +3588,11 @@
         <v>2</v>
       </c>
       <c r="E58" s="5"/>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F58" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
         <v>38</v>
       </c>
@@ -3373,8 +3606,11 @@
         <v>2</v>
       </c>
       <c r="E59" s="5"/>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F59" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>39</v>
       </c>
@@ -3388,8 +3624,11 @@
         <v>2</v>
       </c>
       <c r="E60" s="5"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F60" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>40</v>
       </c>
@@ -3403,8 +3642,11 @@
         <v>2</v>
       </c>
       <c r="E61" s="5"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F61" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>41</v>
       </c>
@@ -3418,8 +3660,11 @@
         <v>2</v>
       </c>
       <c r="E62" s="5"/>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F62" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>42</v>
       </c>
@@ -3433,8 +3678,11 @@
         <v>2</v>
       </c>
       <c r="E63" s="5"/>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F63" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
         <v>43</v>
       </c>
@@ -3448,8 +3696,11 @@
         <v>2</v>
       </c>
       <c r="E64" s="5"/>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F64" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
         <v>44</v>
       </c>
@@ -3463,8 +3714,11 @@
         <v>2</v>
       </c>
       <c r="E65" s="5"/>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F65" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
         <v>46</v>
       </c>
@@ -3478,8 +3732,11 @@
         <v>2</v>
       </c>
       <c r="E66" s="5"/>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F66" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
         <v>47</v>
       </c>
@@ -3493,8 +3750,11 @@
         <v>2</v>
       </c>
       <c r="E67" s="5"/>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F67" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
         <v>48</v>
       </c>
@@ -3508,8 +3768,11 @@
         <v>2</v>
       </c>
       <c r="E68" s="5"/>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F68" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
         <v>57</v>
       </c>
@@ -3523,8 +3786,11 @@
         <v>2</v>
       </c>
       <c r="E69" s="5"/>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F69" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>61</v>
       </c>
@@ -3538,8 +3804,11 @@
         <v>2</v>
       </c>
       <c r="E70" s="5"/>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F70" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
         <v>49</v>
       </c>
@@ -3553,8 +3822,11 @@
         <v>2</v>
       </c>
       <c r="E71" s="5"/>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F71" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
         <v>50</v>
       </c>
@@ -3568,8 +3840,11 @@
         <v>2</v>
       </c>
       <c r="E72" s="5"/>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F72" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
         <v>53</v>
       </c>
@@ -3583,8 +3858,11 @@
         <v>2</v>
       </c>
       <c r="E73" s="5"/>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F73" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
         <v>54</v>
       </c>
@@ -3598,8 +3876,11 @@
         <v>2</v>
       </c>
       <c r="E74" s="5"/>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F74" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
         <v>60</v>
       </c>
@@ -3613,8 +3894,11 @@
         <v>2</v>
       </c>
       <c r="E75" s="5"/>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F75" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
         <v>62</v>
       </c>
@@ -3628,10 +3912,13 @@
         <v>2</v>
       </c>
       <c r="E76" s="5"/>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F76" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="B77" s="5">
         <v>1</v>
@@ -3643,12 +3930,15 @@
         <v>2</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="B78" s="5">
         <v>1</v>
@@ -3660,12 +3950,15 @@
         <v>2</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+        <v>251</v>
+      </c>
+      <c r="F78" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="B79" s="5">
         <v>1</v>
@@ -3677,8 +3970,11 @@
         <v>2</v>
       </c>
       <c r="E79" s="5"/>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F79" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
         <v>58</v>
       </c>
@@ -3692,8 +3988,11 @@
         <v>2</v>
       </c>
       <c r="E80" s="5"/>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F80" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
         <v>63</v>
       </c>
@@ -3707,8 +4006,11 @@
         <v>2</v>
       </c>
       <c r="E81" s="5"/>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F81" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
         <v>17</v>
       </c>
@@ -3722,8 +4024,11 @@
         <v>2</v>
       </c>
       <c r="E82" s="5"/>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F82" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
         <v>37</v>
       </c>
@@ -3737,10 +4042,13 @@
         <v>2</v>
       </c>
       <c r="E83" s="5"/>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F83" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="B84" s="5">
         <v>1</v>
@@ -3752,12 +4060,15 @@
         <v>2</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+      <c r="F84" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="B85" s="5">
         <v>1</v>
@@ -3769,12 +4080,15 @@
         <v>2</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+        <v>236</v>
+      </c>
+      <c r="F85" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="B86" s="5">
         <v>1</v>
@@ -3786,91 +4100,109 @@
         <v>2</v>
       </c>
       <c r="E86" s="5"/>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F86" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="B87" s="5">
         <v>1</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D87" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E87" s="5"/>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F87" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="B88" s="5">
         <v>1</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D88" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+      <c r="F88" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="B89" s="5">
         <v>1</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="D89" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+        <v>510</v>
+      </c>
+      <c r="F89" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="B90" s="5">
         <v>1</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="D90" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="B91" s="5">
         <v>1</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="D91" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+      <c r="F91" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
         <v>55</v>
       </c>
@@ -3884,8 +4216,11 @@
         <v>2</v>
       </c>
       <c r="E92" s="5"/>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F92" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
         <v>56</v>
       </c>
@@ -3899,8 +4234,11 @@
         <v>2</v>
       </c>
       <c r="E93" s="5"/>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F93" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
         <v>13</v>
       </c>
@@ -3914,25 +4252,31 @@
         <v>2</v>
       </c>
       <c r="E94" s="5"/>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F94" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="B95" s="5">
         <v>1</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="D95" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+      <c r="F95" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
         <v>0</v>
       </c>
@@ -3940,12 +4284,15 @@
         <v>1</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>520</v>
+        <v>509</v>
       </c>
       <c r="D96" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E96" s="5"/>
+      <c r="F96" s="5" t="s">
+        <v>533</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -3960,90 +4307,90 @@
     <hyperlink ref="A10" r:id="rId9" xr:uid="{F0968ADA-E23A-41D1-9BB2-797E03EC25B6}"/>
     <hyperlink ref="A11" r:id="rId10" xr:uid="{1F680899-9D5F-4542-8250-D01AF8F46062}"/>
     <hyperlink ref="A55" r:id="rId11" xr:uid="{1EFD7985-544E-4930-92F7-CA5CF62C1F5C}"/>
-    <hyperlink ref="A12" r:id="rId12" xr:uid="{22E0C0F8-8E46-418B-A356-F46EEAD78C89}"/>
-    <hyperlink ref="A13" r:id="rId13" xr:uid="{C24CB84F-7D35-4E81-9A40-AF10EF06DBBF}"/>
-    <hyperlink ref="A54" r:id="rId14" xr:uid="{F21F4C3D-1E73-4B98-AE23-DDE0F097A69A}"/>
-    <hyperlink ref="A14" r:id="rId15" xr:uid="{15F4636C-626C-427C-8BB4-768D654E4DEA}"/>
-    <hyperlink ref="A15" r:id="rId16" xr:uid="{831852BF-0353-48D8-802D-D5ADE7E5704A}"/>
-    <hyperlink ref="A16" r:id="rId17" xr:uid="{2257648C-0818-4AC8-9D4D-C3EEF4117511}"/>
-    <hyperlink ref="A17" r:id="rId18" xr:uid="{79B25CFB-70AB-4F3C-B33F-1179962C3BE1}"/>
-    <hyperlink ref="A18" r:id="rId19" xr:uid="{B97B6620-0291-4FC8-BD5A-07CC0E7DE530}"/>
-    <hyperlink ref="A19" r:id="rId20" xr:uid="{1159832A-196E-48FC-9CAB-2D23ED5144A2}"/>
-    <hyperlink ref="A20" r:id="rId21" xr:uid="{18BB9D82-86B9-43A7-BA11-AB9C5BEA36F0}"/>
-    <hyperlink ref="A21" r:id="rId22" xr:uid="{FB2C8750-74C9-418F-B1BE-45349AA0673A}"/>
-    <hyperlink ref="A77" r:id="rId23" xr:uid="{B05DDD51-1571-4982-A97E-F4F59D2E1BA4}"/>
-    <hyperlink ref="A28" r:id="rId24" xr:uid="{5601E68F-EE61-48B5-A6F9-A9C930A40586}"/>
-    <hyperlink ref="A90" r:id="rId25" xr:uid="{25D3D708-1A3D-47CC-BFF0-1DE02B83F016}"/>
-    <hyperlink ref="A91" r:id="rId26" xr:uid="{88950493-9C73-410B-B90F-69AA955E72BD}"/>
-    <hyperlink ref="A46" r:id="rId27" xr:uid="{DEC40395-5CC1-4FCF-B47D-6905A94B01D7}"/>
-    <hyperlink ref="A33" r:id="rId28" xr:uid="{167FA7A2-533E-433E-BAA1-A6A4287577D4}"/>
-    <hyperlink ref="A87" r:id="rId29" xr:uid="{08587152-9FEA-4D67-9C1F-3A77BB7BE2AA}"/>
-    <hyperlink ref="A88" r:id="rId30" xr:uid="{A4C41886-401E-43FE-9E21-C232B065E1B9}"/>
-    <hyperlink ref="A89" r:id="rId31" xr:uid="{6853F4A4-2E8B-421D-8CB8-3D37EBFD7884}"/>
-    <hyperlink ref="A50" r:id="rId32" xr:uid="{52823431-3BC6-4027-BEBA-C785AF6A161A}"/>
-    <hyperlink ref="A75" r:id="rId33" xr:uid="{F58A47B3-C93D-46C1-BB5F-2AB56BAF236B}"/>
-    <hyperlink ref="A73" r:id="rId34" xr:uid="{787BFB3C-7270-467B-AE62-FFFC05F304FF}"/>
-    <hyperlink ref="A74" r:id="rId35" xr:uid="{D007EE63-7D08-49DF-81AE-6E27F0169413}"/>
-    <hyperlink ref="A23" r:id="rId36" xr:uid="{2575B273-E12A-44E5-946E-C16AA108F5B4}"/>
-    <hyperlink ref="A22" r:id="rId37" xr:uid="{9BC20C71-80F6-4A5D-AA53-DBDBC038187D}"/>
-    <hyperlink ref="A24" r:id="rId38" xr:uid="{CA415CC2-FDB4-42A8-8DC2-420328FFBC47}"/>
-    <hyperlink ref="A25" r:id="rId39" xr:uid="{13E71A26-2CB4-43F2-AB0F-B267C0F57ECF}"/>
-    <hyperlink ref="A26" r:id="rId40" xr:uid="{77F1D45A-9EE4-4644-8DAA-E454DF215CA5}"/>
-    <hyperlink ref="A27" r:id="rId41" xr:uid="{4A9E5AA5-0B7B-48FE-84B7-982EF7488400}"/>
-    <hyperlink ref="A29" r:id="rId42" xr:uid="{EC0F2160-1E5A-415E-9EE1-71E913A4229D}"/>
-    <hyperlink ref="A30" r:id="rId43" xr:uid="{68437BB2-9D19-4187-8BFE-3D4904641058}"/>
-    <hyperlink ref="A31" r:id="rId44" xr:uid="{5083E1E7-9D8B-4D01-B258-F868E4C9BBE4}"/>
-    <hyperlink ref="A32" r:id="rId45" xr:uid="{78C33DEC-077D-4D54-ABDB-5DB77E7D6D2C}"/>
-    <hyperlink ref="A34" r:id="rId46" xr:uid="{5BF81DEF-9895-4C1F-B79F-EB6829E95A26}"/>
-    <hyperlink ref="A35" r:id="rId47" xr:uid="{D37BFBF2-3171-4B9F-AE2C-7DAD2972D429}"/>
-    <hyperlink ref="A36" r:id="rId48" xr:uid="{0BBA3A06-80FC-41CA-B2FE-0B75CC9DD017}"/>
-    <hyperlink ref="A37" r:id="rId49" xr:uid="{03828235-8336-4D71-8C3D-1EB04789A0C3}"/>
-    <hyperlink ref="A38" r:id="rId50" xr:uid="{D5E2781E-1F59-49B6-B089-9B69F96888FD}"/>
-    <hyperlink ref="A39" r:id="rId51" xr:uid="{08B7EC38-9A88-48FE-81C6-1FF4FF2E43C0}"/>
-    <hyperlink ref="A40" r:id="rId52" xr:uid="{B706A9E8-0577-4A3E-BF1A-02C4FEBCE30C}"/>
-    <hyperlink ref="A41" r:id="rId53" xr:uid="{1A3666E1-FFD9-48F6-8157-2D8ACE72F75E}"/>
-    <hyperlink ref="A42" r:id="rId54" xr:uid="{8BAADFE2-A09D-4734-9202-E237B811E19B}"/>
-    <hyperlink ref="A43" r:id="rId55" xr:uid="{9FB44828-C4AE-411B-9C64-5CD5294C984F}"/>
-    <hyperlink ref="A44" r:id="rId56" xr:uid="{9B809D6B-F315-457D-81D9-3E10C8B2313A}"/>
-    <hyperlink ref="A45" r:id="rId57" xr:uid="{A44A2E68-65EE-4567-8FC8-49F583A32282}"/>
-    <hyperlink ref="A47" r:id="rId58" xr:uid="{01DC45B6-5848-43ED-9488-76E3765F11C9}"/>
-    <hyperlink ref="A48" r:id="rId59" xr:uid="{FA2F87BC-D9FE-47B7-848C-D8F934AD179E}"/>
-    <hyperlink ref="A49" r:id="rId60" xr:uid="{D265B01C-1209-4E28-86C3-658FC23398A6}"/>
-    <hyperlink ref="A51" r:id="rId61" xr:uid="{D9A757A3-CE3C-4529-A042-1AF703E887E6}"/>
-    <hyperlink ref="A56" r:id="rId62" xr:uid="{E67316B9-8C66-4974-8987-2952637D411E}"/>
-    <hyperlink ref="A57" r:id="rId63" xr:uid="{206A6062-72FA-4CE5-AB02-1AB0777D93DD}"/>
-    <hyperlink ref="A58" r:id="rId64" xr:uid="{06668E90-566A-4F7D-AD5A-F7E3805B465B}"/>
-    <hyperlink ref="A59" r:id="rId65" xr:uid="{BDF87DB2-CF6C-4F34-A3C6-7A40EA4023D1}"/>
-    <hyperlink ref="A60" r:id="rId66" xr:uid="{17B5EB64-17DC-4629-B910-7116CF0235D6}"/>
-    <hyperlink ref="A61" r:id="rId67" xr:uid="{5E3EDFC3-BAA3-47C9-AC34-A89A409A78C8}"/>
-    <hyperlink ref="A62" r:id="rId68" xr:uid="{AD7AB9AB-6FE6-4F33-AE7C-7161C81EA64D}"/>
-    <hyperlink ref="A63" r:id="rId69" xr:uid="{1DB69D57-B824-4331-B39E-FEB59936CA1A}"/>
-    <hyperlink ref="A64" r:id="rId70" xr:uid="{24A21151-0562-4683-A56D-94B3E59FB6BF}"/>
-    <hyperlink ref="A65" r:id="rId71" xr:uid="{355171A9-954C-4549-9C4F-57F09066BD12}"/>
-    <hyperlink ref="A66" r:id="rId72" xr:uid="{5F7A2291-B7F0-4441-9333-FE883FEB384E}"/>
-    <hyperlink ref="A67" r:id="rId73" xr:uid="{A170072D-EAC2-4E14-9FD2-27311DEA2853}"/>
-    <hyperlink ref="A68" r:id="rId74" xr:uid="{6B7DEA75-AC16-4071-A069-159D505E675A}"/>
-    <hyperlink ref="A69" r:id="rId75" xr:uid="{6B546662-16C7-4C28-A7BB-DBE1ED1FA44D}"/>
-    <hyperlink ref="A70" r:id="rId76" xr:uid="{302214F2-CEF0-40D3-9938-414BAFBA5115}"/>
-    <hyperlink ref="A71" r:id="rId77" xr:uid="{1F72C71F-D517-4788-A77F-0FCBEE25C5A3}"/>
-    <hyperlink ref="A72" r:id="rId78" xr:uid="{870528D3-3AD6-4C50-A066-367CE8476AD0}"/>
-    <hyperlink ref="A76" r:id="rId79" xr:uid="{A3389C09-1EE7-4FDC-BF97-B131864DA101}"/>
-    <hyperlink ref="A78" r:id="rId80" xr:uid="{2EB0CB00-0F88-4942-A871-2F4BAA303058}"/>
-    <hyperlink ref="A79" r:id="rId81" xr:uid="{8889D5DC-A330-4A65-AF17-71183754BDC4}"/>
-    <hyperlink ref="A80" r:id="rId82" xr:uid="{6396BEE4-0B1B-400B-ABE6-C6FE06FD02BC}"/>
-    <hyperlink ref="A81" r:id="rId83" xr:uid="{7CFAA56C-1D87-4EF6-9A8C-DE3F0CE5146C}"/>
-    <hyperlink ref="A82" r:id="rId84" xr:uid="{C35A8D28-7ACD-4910-B4A3-DC9A3E9EDE99}"/>
-    <hyperlink ref="A83" r:id="rId85" xr:uid="{BB1E212A-FCA1-4FFE-927E-D6268F0C86A2}"/>
-    <hyperlink ref="A84" r:id="rId86" xr:uid="{A30A5BD7-E4A7-493E-8A1C-C0D9ADE6BC7B}"/>
-    <hyperlink ref="A86" r:id="rId87" xr:uid="{E3E68DE9-1C9F-4B3E-90B7-1B02A6992EE9}"/>
-    <hyperlink ref="A85" r:id="rId88" xr:uid="{B4BFC9B4-613D-4855-96D4-FD4A6595AA3D}"/>
-    <hyperlink ref="A92" r:id="rId89" xr:uid="{BCE175F5-4928-4DD0-864B-3465A4BCAE96}"/>
-    <hyperlink ref="A93" r:id="rId90" xr:uid="{7D16CA98-805D-41F7-A16C-E260B8A8A675}"/>
-    <hyperlink ref="A94" r:id="rId91" xr:uid="{22D095F2-F983-47F3-AFE7-95BBCCD19B39}"/>
-    <hyperlink ref="A95" r:id="rId92" xr:uid="{F537F5C9-0F6E-4895-9E40-2E7BF20812FF}"/>
-    <hyperlink ref="A96" r:id="rId93" xr:uid="{5C382073-3AE5-432D-B737-A099200871D8}"/>
-    <hyperlink ref="A2" r:id="rId94" xr:uid="{DF51F8E9-1CC4-40BE-AFA5-8D05D17C7E25}"/>
-    <hyperlink ref="A3" r:id="rId95" xr:uid="{1BD211AF-ADAA-4F92-A932-869557977E19}"/>
+    <hyperlink ref="A13" r:id="rId12" xr:uid="{C24CB84F-7D35-4E81-9A40-AF10EF06DBBF}"/>
+    <hyperlink ref="A54" r:id="rId13" xr:uid="{F21F4C3D-1E73-4B98-AE23-DDE0F097A69A}"/>
+    <hyperlink ref="A14" r:id="rId14" xr:uid="{15F4636C-626C-427C-8BB4-768D654E4DEA}"/>
+    <hyperlink ref="A15" r:id="rId15" xr:uid="{831852BF-0353-48D8-802D-D5ADE7E5704A}"/>
+    <hyperlink ref="A16" r:id="rId16" xr:uid="{2257648C-0818-4AC8-9D4D-C3EEF4117511}"/>
+    <hyperlink ref="A17" r:id="rId17" xr:uid="{79B25CFB-70AB-4F3C-B33F-1179962C3BE1}"/>
+    <hyperlink ref="A18" r:id="rId18" xr:uid="{B97B6620-0291-4FC8-BD5A-07CC0E7DE530}"/>
+    <hyperlink ref="A19" r:id="rId19" xr:uid="{1159832A-196E-48FC-9CAB-2D23ED5144A2}"/>
+    <hyperlink ref="A20" r:id="rId20" xr:uid="{18BB9D82-86B9-43A7-BA11-AB9C5BEA36F0}"/>
+    <hyperlink ref="A21" r:id="rId21" xr:uid="{FB2C8750-74C9-418F-B1BE-45349AA0673A}"/>
+    <hyperlink ref="A77" r:id="rId22" xr:uid="{B05DDD51-1571-4982-A97E-F4F59D2E1BA4}"/>
+    <hyperlink ref="A28" r:id="rId23" xr:uid="{5601E68F-EE61-48B5-A6F9-A9C930A40586}"/>
+    <hyperlink ref="A90" r:id="rId24" xr:uid="{25D3D708-1A3D-47CC-BFF0-1DE02B83F016}"/>
+    <hyperlink ref="A91" r:id="rId25" xr:uid="{88950493-9C73-410B-B90F-69AA955E72BD}"/>
+    <hyperlink ref="A46" r:id="rId26" xr:uid="{DEC40395-5CC1-4FCF-B47D-6905A94B01D7}"/>
+    <hyperlink ref="A33" r:id="rId27" xr:uid="{167FA7A2-533E-433E-BAA1-A6A4287577D4}"/>
+    <hyperlink ref="A87" r:id="rId28" xr:uid="{08587152-9FEA-4D67-9C1F-3A77BB7BE2AA}"/>
+    <hyperlink ref="A88" r:id="rId29" xr:uid="{A4C41886-401E-43FE-9E21-C232B065E1B9}"/>
+    <hyperlink ref="A89" r:id="rId30" xr:uid="{6853F4A4-2E8B-421D-8CB8-3D37EBFD7884}"/>
+    <hyperlink ref="A50" r:id="rId31" xr:uid="{52823431-3BC6-4027-BEBA-C785AF6A161A}"/>
+    <hyperlink ref="A75" r:id="rId32" xr:uid="{F58A47B3-C93D-46C1-BB5F-2AB56BAF236B}"/>
+    <hyperlink ref="A73" r:id="rId33" xr:uid="{787BFB3C-7270-467B-AE62-FFFC05F304FF}"/>
+    <hyperlink ref="A74" r:id="rId34" xr:uid="{D007EE63-7D08-49DF-81AE-6E27F0169413}"/>
+    <hyperlink ref="A23" r:id="rId35" xr:uid="{2575B273-E12A-44E5-946E-C16AA108F5B4}"/>
+    <hyperlink ref="A22" r:id="rId36" xr:uid="{9BC20C71-80F6-4A5D-AA53-DBDBC038187D}"/>
+    <hyperlink ref="A24" r:id="rId37" xr:uid="{CA415CC2-FDB4-42A8-8DC2-420328FFBC47}"/>
+    <hyperlink ref="A25" r:id="rId38" xr:uid="{13E71A26-2CB4-43F2-AB0F-B267C0F57ECF}"/>
+    <hyperlink ref="A26" r:id="rId39" xr:uid="{77F1D45A-9EE4-4644-8DAA-E454DF215CA5}"/>
+    <hyperlink ref="A27" r:id="rId40" xr:uid="{4A9E5AA5-0B7B-48FE-84B7-982EF7488400}"/>
+    <hyperlink ref="A29" r:id="rId41" xr:uid="{EC0F2160-1E5A-415E-9EE1-71E913A4229D}"/>
+    <hyperlink ref="A30" r:id="rId42" xr:uid="{68437BB2-9D19-4187-8BFE-3D4904641058}"/>
+    <hyperlink ref="A31" r:id="rId43" xr:uid="{5083E1E7-9D8B-4D01-B258-F868E4C9BBE4}"/>
+    <hyperlink ref="A32" r:id="rId44" xr:uid="{78C33DEC-077D-4D54-ABDB-5DB77E7D6D2C}"/>
+    <hyperlink ref="A34" r:id="rId45" xr:uid="{5BF81DEF-9895-4C1F-B79F-EB6829E95A26}"/>
+    <hyperlink ref="A35" r:id="rId46" xr:uid="{D37BFBF2-3171-4B9F-AE2C-7DAD2972D429}"/>
+    <hyperlink ref="A36" r:id="rId47" xr:uid="{0BBA3A06-80FC-41CA-B2FE-0B75CC9DD017}"/>
+    <hyperlink ref="A37" r:id="rId48" xr:uid="{03828235-8336-4D71-8C3D-1EB04789A0C3}"/>
+    <hyperlink ref="A38" r:id="rId49" xr:uid="{D5E2781E-1F59-49B6-B089-9B69F96888FD}"/>
+    <hyperlink ref="A39" r:id="rId50" xr:uid="{08B7EC38-9A88-48FE-81C6-1FF4FF2E43C0}"/>
+    <hyperlink ref="A40" r:id="rId51" xr:uid="{B706A9E8-0577-4A3E-BF1A-02C4FEBCE30C}"/>
+    <hyperlink ref="A41" r:id="rId52" xr:uid="{1A3666E1-FFD9-48F6-8157-2D8ACE72F75E}"/>
+    <hyperlink ref="A42" r:id="rId53" xr:uid="{8BAADFE2-A09D-4734-9202-E237B811E19B}"/>
+    <hyperlink ref="A43" r:id="rId54" xr:uid="{9FB44828-C4AE-411B-9C64-5CD5294C984F}"/>
+    <hyperlink ref="A44" r:id="rId55" xr:uid="{9B809D6B-F315-457D-81D9-3E10C8B2313A}"/>
+    <hyperlink ref="A45" r:id="rId56" xr:uid="{A44A2E68-65EE-4567-8FC8-49F583A32282}"/>
+    <hyperlink ref="A47" r:id="rId57" xr:uid="{01DC45B6-5848-43ED-9488-76E3765F11C9}"/>
+    <hyperlink ref="A48" r:id="rId58" xr:uid="{FA2F87BC-D9FE-47B7-848C-D8F934AD179E}"/>
+    <hyperlink ref="A49" r:id="rId59" xr:uid="{D265B01C-1209-4E28-86C3-658FC23398A6}"/>
+    <hyperlink ref="A51" r:id="rId60" xr:uid="{D9A757A3-CE3C-4529-A042-1AF703E887E6}"/>
+    <hyperlink ref="A56" r:id="rId61" xr:uid="{E67316B9-8C66-4974-8987-2952637D411E}"/>
+    <hyperlink ref="A57" r:id="rId62" xr:uid="{206A6062-72FA-4CE5-AB02-1AB0777D93DD}"/>
+    <hyperlink ref="A58" r:id="rId63" xr:uid="{06668E90-566A-4F7D-AD5A-F7E3805B465B}"/>
+    <hyperlink ref="A59" r:id="rId64" xr:uid="{BDF87DB2-CF6C-4F34-A3C6-7A40EA4023D1}"/>
+    <hyperlink ref="A60" r:id="rId65" xr:uid="{17B5EB64-17DC-4629-B910-7116CF0235D6}"/>
+    <hyperlink ref="A61" r:id="rId66" xr:uid="{5E3EDFC3-BAA3-47C9-AC34-A89A409A78C8}"/>
+    <hyperlink ref="A62" r:id="rId67" xr:uid="{AD7AB9AB-6FE6-4F33-AE7C-7161C81EA64D}"/>
+    <hyperlink ref="A63" r:id="rId68" xr:uid="{1DB69D57-B824-4331-B39E-FEB59936CA1A}"/>
+    <hyperlink ref="A64" r:id="rId69" xr:uid="{24A21151-0562-4683-A56D-94B3E59FB6BF}"/>
+    <hyperlink ref="A65" r:id="rId70" xr:uid="{355171A9-954C-4549-9C4F-57F09066BD12}"/>
+    <hyperlink ref="A66" r:id="rId71" xr:uid="{5F7A2291-B7F0-4441-9333-FE883FEB384E}"/>
+    <hyperlink ref="A67" r:id="rId72" xr:uid="{A170072D-EAC2-4E14-9FD2-27311DEA2853}"/>
+    <hyperlink ref="A68" r:id="rId73" xr:uid="{6B7DEA75-AC16-4071-A069-159D505E675A}"/>
+    <hyperlink ref="A69" r:id="rId74" xr:uid="{6B546662-16C7-4C28-A7BB-DBE1ED1FA44D}"/>
+    <hyperlink ref="A70" r:id="rId75" xr:uid="{302214F2-CEF0-40D3-9938-414BAFBA5115}"/>
+    <hyperlink ref="A71" r:id="rId76" xr:uid="{1F72C71F-D517-4788-A77F-0FCBEE25C5A3}"/>
+    <hyperlink ref="A72" r:id="rId77" xr:uid="{870528D3-3AD6-4C50-A066-367CE8476AD0}"/>
+    <hyperlink ref="A76" r:id="rId78" xr:uid="{A3389C09-1EE7-4FDC-BF97-B131864DA101}"/>
+    <hyperlink ref="A78" r:id="rId79" xr:uid="{2EB0CB00-0F88-4942-A871-2F4BAA303058}"/>
+    <hyperlink ref="A79" r:id="rId80" xr:uid="{8889D5DC-A330-4A65-AF17-71183754BDC4}"/>
+    <hyperlink ref="A80" r:id="rId81" xr:uid="{6396BEE4-0B1B-400B-ABE6-C6FE06FD02BC}"/>
+    <hyperlink ref="A81" r:id="rId82" xr:uid="{7CFAA56C-1D87-4EF6-9A8C-DE3F0CE5146C}"/>
+    <hyperlink ref="A82" r:id="rId83" xr:uid="{C35A8D28-7ACD-4910-B4A3-DC9A3E9EDE99}"/>
+    <hyperlink ref="A83" r:id="rId84" xr:uid="{BB1E212A-FCA1-4FFE-927E-D6268F0C86A2}"/>
+    <hyperlink ref="A84" r:id="rId85" xr:uid="{A30A5BD7-E4A7-493E-8A1C-C0D9ADE6BC7B}"/>
+    <hyperlink ref="A86" r:id="rId86" xr:uid="{E3E68DE9-1C9F-4B3E-90B7-1B02A6992EE9}"/>
+    <hyperlink ref="A85" r:id="rId87" xr:uid="{B4BFC9B4-613D-4855-96D4-FD4A6595AA3D}"/>
+    <hyperlink ref="A92" r:id="rId88" xr:uid="{BCE175F5-4928-4DD0-864B-3465A4BCAE96}"/>
+    <hyperlink ref="A93" r:id="rId89" xr:uid="{7D16CA98-805D-41F7-A16C-E260B8A8A675}"/>
+    <hyperlink ref="A94" r:id="rId90" xr:uid="{22D095F2-F983-47F3-AFE7-95BBCCD19B39}"/>
+    <hyperlink ref="A95" r:id="rId91" xr:uid="{F537F5C9-0F6E-4895-9E40-2E7BF20812FF}"/>
+    <hyperlink ref="A96" r:id="rId92" xr:uid="{5C382073-3AE5-432D-B737-A099200871D8}"/>
+    <hyperlink ref="A2" r:id="rId93" xr:uid="{DF51F8E9-1CC4-40BE-AFA5-8D05D17C7E25}"/>
+    <hyperlink ref="A3" r:id="rId94" xr:uid="{1BD211AF-ADAA-4F92-A932-869557977E19}"/>
+    <hyperlink ref="A12" r:id="rId95" xr:uid="{22E0C0F8-8E46-418B-A356-F46EEAD78C89}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
@@ -4054,7 +4401,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96254920-D845-4B30-A00A-B9D0C3F1CE7A}">
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="55.7109375" customWidth="1"/>
@@ -4064,7 +4411,7 @@
     <col min="5" max="5" width="20.85546875" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>73</v>
       </c>
@@ -4072,7 +4419,7 @@
         <v>72</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>74</v>
@@ -4080,93 +4427,111 @@
       <c r="E1" s="9" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="9" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="B2" s="5">
         <v>1</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>309</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="B3" s="5">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>310</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="B4" s="5">
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="B5" s="5">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>313</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="B6" s="5">
         <v>1</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>314</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>8</v>
       </c>
@@ -4180,12 +4545,15 @@
         <v>4</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>177</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="B8" s="5">
         <v>1</v>
@@ -4197,10 +4565,13 @@
         <v>4</v>
       </c>
       <c r="E8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F8" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="B9" s="5">
         <v>1</v>
@@ -4212,12 +4583,15 @@
         <v>4</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="B10" s="5">
         <v>1</v>
@@ -4229,12 +4603,15 @@
         <v>4</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="B11" s="5">
         <v>1</v>
@@ -4246,12 +4623,15 @@
         <v>4</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>464</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B12" s="5">
         <v>1</v>
@@ -4263,12 +4643,15 @@
         <v>4</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="B13" s="5">
         <v>1</v>
@@ -4280,12 +4663,15 @@
         <v>4</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="B14" s="5">
         <v>1</v>
@@ -4297,12 +4683,15 @@
         <v>4</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>180</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="B15" s="5">
         <v>1</v>
@@ -4314,12 +4703,15 @@
         <v>4</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="B16" s="5">
         <v>1</v>
@@ -4331,12 +4723,15 @@
         <v>4</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>182</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="B17" s="5">
         <v>1</v>
@@ -4348,12 +4743,15 @@
         <v>4</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="B18" s="5">
         <v>1</v>
@@ -4365,12 +4763,15 @@
         <v>4</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>191</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="B19" s="5">
         <v>1</v>
@@ -4382,12 +4783,15 @@
         <v>4</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>193</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="B20" s="5">
         <v>1</v>
@@ -4399,10 +4803,13 @@
         <v>4</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>202</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>69</v>
       </c>
@@ -4414,12 +4821,15 @@
         <v>4</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+        <v>399</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="B22" s="5">
         <v>1</v>
@@ -4431,10 +4841,13 @@
         <v>4</v>
       </c>
       <c r="E22" s="5"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="B23" s="5">
         <v>1</v>
@@ -4446,12 +4859,15 @@
         <v>4</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+        <v>455</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="B24" s="5">
         <v>1</v>
@@ -4463,10 +4879,13 @@
         <v>4</v>
       </c>
       <c r="E24" s="5"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="B25" s="5">
         <v>1</v>
@@ -4478,378 +4897,447 @@
         <v>4</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>460</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="B26" s="5">
         <v>1</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="D26" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="B27" s="5">
         <v>1</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="D27" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>226</v>
-      </c>
       <c r="B28" s="5">
         <v>1</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="D28" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>217</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="B29" s="5">
         <v>1</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+        <v>219</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="B30" s="5">
         <v>1</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <v>221</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="B31" s="5">
+        <v>1</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="B32" s="5">
+        <v>1</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E32" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="B33" s="5">
+        <v>1</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="B34" s="5">
+        <v>1</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E34" s="5" t="s">
+        <v>268</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="B35" s="5">
+        <v>1</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="B36" s="5">
+        <v>1</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="B37" s="5">
+        <v>1</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B38" s="5">
+        <v>1</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="B39" s="5">
+        <v>1</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E39" s="5" t="s">
+        <v>288</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B40" s="5">
+        <v>1</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E40" s="5" t="s">
+        <v>290</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B41" s="5">
+        <v>1</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E41" s="5" t="s">
+        <v>291</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="B42" s="5">
+        <v>1</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="B31" s="5">
-        <v>1</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E31" s="5" t="s">
+      <c r="B43" s="5">
+        <v>1</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E43" s="5" t="s">
         <v>337</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="B32" s="5">
-        <v>1</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D32" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="B33" s="5">
-        <v>1</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D33" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E33" s="5"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="B34" s="5">
-        <v>1</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D34" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="B35" s="5">
-        <v>1</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D35" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="B36" s="5">
-        <v>1</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D36" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E36" s="5"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="B37" s="5">
-        <v>1</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D37" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E37" s="5"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="B38" s="5">
-        <v>1</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D38" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E38" s="5"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B39" s="5">
-        <v>1</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D39" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="B40" s="5">
-        <v>1</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D40" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E40" s="5" t="s">
+      <c r="F43" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="B44" s="5">
+        <v>1</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E44" s="5" t="s">
+        <v>452</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
         <v>300</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="B41" s="5">
-        <v>1</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D41" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E41" s="5" t="s">
+      <c r="B45" s="5">
+        <v>1</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="B42" s="5">
-        <v>1</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E42" s="6" t="s">
+      <c r="D45" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E45" s="5" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="B43" s="5">
-        <v>1</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="B44" s="5">
-        <v>1</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="B45" s="5">
-        <v>1</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F45" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="B46" s="5">
         <v>1</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+        <v>304</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="B47" s="5">
         <v>1</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+        <v>306</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="B48" s="5">
         <v>1</v>
@@ -4861,12 +5349,15 @@
         <v>2</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>535</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+        <v>524</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="B49" s="5">
         <v>1</v>
@@ -4878,10 +5369,13 @@
         <v>2</v>
       </c>
       <c r="E49" s="5"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F49" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="B50" s="5">
         <v>1</v>
@@ -4893,10 +5387,13 @@
         <v>2</v>
       </c>
       <c r="E50" s="5"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F50" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="B51" s="5">
         <v>1</v>
@@ -4908,10 +5405,13 @@
         <v>2</v>
       </c>
       <c r="E51" s="5"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F51" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="B52" s="5">
         <v>1</v>
@@ -4923,10 +5423,13 @@
         <v>2</v>
       </c>
       <c r="E52" s="5"/>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F52" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="B53" s="5">
         <v>1</v>
@@ -4938,12 +5441,15 @@
         <v>2</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+        <v>525</v>
+      </c>
+      <c r="F53" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="B54" s="5">
         <v>1</v>
@@ -4955,10 +5461,13 @@
         <v>2</v>
       </c>
       <c r="E54" s="5"/>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F54" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="B55" s="5">
         <v>1</v>
@@ -4970,12 +5479,15 @@
         <v>2</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="B56" s="5">
         <v>1</v>
@@ -4987,10 +5499,13 @@
         <v>2</v>
       </c>
       <c r="E56" s="5"/>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F56" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="B57" s="5">
         <v>1</v>
@@ -5002,10 +5517,13 @@
         <v>2</v>
       </c>
       <c r="E57" s="5"/>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F57" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="B58" s="5">
         <v>1</v>
@@ -5017,10 +5535,13 @@
         <v>2</v>
       </c>
       <c r="E58" s="5"/>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F58" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="B59" s="5">
         <v>1</v>
@@ -5032,10 +5553,13 @@
         <v>2</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
         <v>65</v>
       </c>
@@ -5049,8 +5573,11 @@
         <v>2</v>
       </c>
       <c r="E60" s="5"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F60" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
         <v>45</v>
       </c>
@@ -5064,8 +5591,11 @@
         <v>2</v>
       </c>
       <c r="E61" s="5"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F61" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
         <v>1</v>
       </c>
@@ -5079,10 +5609,13 @@
         <v>2</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>537</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+        <v>526</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
         <v>51</v>
       </c>
@@ -5096,10 +5629,13 @@
         <v>2</v>
       </c>
       <c r="E63" s="5"/>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F63" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="B64" s="5">
         <v>1</v>
@@ -5111,12 +5647,15 @@
         <v>2</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B65" s="5">
         <v>1</v>
@@ -5128,12 +5667,15 @@
         <v>2</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="B66" s="5">
         <v>1</v>
@@ -5145,10 +5687,13 @@
         <v>2</v>
       </c>
       <c r="E66" s="5"/>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F66" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="B67" s="5">
         <v>1</v>
@@ -5160,12 +5705,15 @@
         <v>2</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+        <v>196</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="B68" s="5">
         <v>1</v>
@@ -5177,12 +5725,15 @@
         <v>2</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="B69" s="5">
         <v>1</v>
@@ -5194,12 +5745,15 @@
         <v>2</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="B70" s="5">
         <v>1</v>
@@ -5211,12 +5765,15 @@
         <v>2</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+        <v>204</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="B71" s="5">
         <v>1</v>
@@ -5228,10 +5785,13 @@
         <v>2</v>
       </c>
       <c r="E71" s="5"/>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F71" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="B72" s="5">
         <v>1</v>
@@ -5243,10 +5803,13 @@
         <v>2</v>
       </c>
       <c r="E72" s="5"/>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F72" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="B73" s="5">
         <v>1</v>
@@ -5258,80 +5821,95 @@
         <v>2</v>
       </c>
       <c r="E73" s="5"/>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F73" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="B74" s="5">
         <v>1</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="D74" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="B75" s="5">
         <v>1</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="D75" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E75" s="5"/>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F75" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="B76" s="5">
         <v>1</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="D76" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E76" s="5"/>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F76" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="B77" s="5">
         <v>1</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="D77" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="B78" s="5">
         <v>1</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="D78" s="5" t="s">
         <v>2</v>
@@ -5339,168 +5917,201 @@
       <c r="E78" s="5" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F78" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="B79" s="5">
         <v>1</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="D79" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E79" s="5"/>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F79" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="B80" s="5">
+        <v>1</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E80" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F80" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B81" s="5">
+        <v>1</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E81" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="B82" s="5">
+        <v>1</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E82" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="F82" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B83" s="5">
+        <v>1</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E83" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="B80" s="5">
-        <v>1</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D80" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="B81" s="5">
-        <v>1</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D81" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="B82" s="5">
-        <v>1</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D82" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B83" s="5">
-        <v>1</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D83" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F83" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="B84" s="5">
         <v>1</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="D84" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+        <v>331</v>
+      </c>
+      <c r="F84" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="B85" s="5">
         <v>1</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="D85" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E85" s="5"/>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F85" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="B86" s="5">
         <v>1</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="D86" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E86" s="5"/>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F86" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="B87" s="5">
         <v>1</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="D87" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="F87" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
       <c r="B88" s="5">
         <v>1</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="D88" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E88" s="5"/>
+      <c r="F88" s="5" t="s">
+        <v>533</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -5601,7 +6212,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8D66C23E-87E5-4813-AF0A-DC21A95E91BE}">
-  <dimension ref="A1:E76"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="69" customWidth="1"/>
@@ -5611,7 +6222,7 @@
     <col min="5" max="5" width="20.140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>73</v>
       </c>
@@ -5619,7 +6230,7 @@
         <v>72</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>74</v>
@@ -5627,8 +6238,11 @@
       <c r="E1" s="9" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="9" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>6</v>
       </c>
@@ -5640,12 +6254,15 @@
         <v>4</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>531</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="B3" s="5">
         <v>1</v>
@@ -5657,12 +6274,15 @@
         <v>4</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>388</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="B4" s="5">
         <v>1</v>
@@ -5674,12 +6294,15 @@
         <v>4</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>390</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="B5" s="5">
         <v>1</v>
@@ -5691,12 +6314,15 @@
         <v>4</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>392</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="B6" s="5">
         <v>1</v>
@@ -5708,142 +6334,169 @@
         <v>4</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>394</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="B7" s="5">
         <v>1</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>447</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="B8" s="5">
         <v>1</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>449</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="B9" s="5">
         <v>1</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E9" s="5"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F9" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="B10" s="5">
         <v>1</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="B11" s="5">
         <v>1</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E11" s="5"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F11" s="10" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="B12" s="5">
         <v>1</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>426</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B13" s="5">
+        <v>1</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>396</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="B13" s="5">
-        <v>1</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="5" t="s">
+      <c r="B14" s="5">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="B14" s="5">
-        <v>1</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F14" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>25</v>
       </c>
@@ -5857,8 +6510,11 @@
         <v>4</v>
       </c>
       <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>10</v>
       </c>
@@ -5872,10 +6528,13 @@
         <v>4</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>527</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>12</v>
       </c>
@@ -5889,10 +6548,13 @@
         <v>4</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>29</v>
       </c>
@@ -5906,12 +6568,15 @@
         <v>4</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>539</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>528</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B19" s="5">
         <v>1</v>
@@ -5923,12 +6588,15 @@
         <v>4</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="B20" s="5">
         <v>1</v>
@@ -5940,12 +6608,15 @@
         <v>4</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>353</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="B21" s="5">
         <v>1</v>
@@ -5957,12 +6628,15 @@
         <v>4</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+        <v>355</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="B22" s="5">
         <v>1</v>
@@ -5974,12 +6648,15 @@
         <v>4</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>357</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="B23" s="5">
         <v>1</v>
@@ -5991,12 +6668,15 @@
         <v>4</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+        <v>359</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="B24" s="5">
         <v>1</v>
@@ -6008,12 +6688,15 @@
         <v>4</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>371</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+        <v>361</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="B25" s="5">
         <v>1</v>
@@ -6025,12 +6708,15 @@
         <v>4</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>373</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+        <v>363</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="B26" s="5">
         <v>1</v>
@@ -6042,12 +6728,15 @@
         <v>4</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+        <v>367</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="B27" s="5">
         <v>1</v>
@@ -6059,12 +6748,15 @@
         <v>4</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+        <v>369</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="B28" s="5">
         <v>1</v>
@@ -6076,10 +6768,13 @@
         <v>4</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>383</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+        <v>373</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>20</v>
       </c>
@@ -6093,10 +6788,13 @@
         <v>4</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>541</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+        <v>530</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>24</v>
       </c>
@@ -6110,10 +6808,13 @@
         <v>4</v>
       </c>
       <c r="E30" s="5"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F30" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="B31" s="5">
         <v>1</v>
@@ -6125,12 +6826,15 @@
         <v>4</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+        <v>343</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="B32" s="5">
         <v>1</v>
@@ -6142,12 +6846,15 @@
         <v>4</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+        <v>345</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="B33" s="5">
         <v>1</v>
@@ -6159,12 +6866,15 @@
         <v>4</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>347</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="B34" s="5">
         <v>1</v>
@@ -6176,12 +6886,15 @@
         <v>4</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+        <v>349</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="B35" s="5">
         <v>1</v>
@@ -6193,12 +6906,15 @@
         <v>4</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+        <v>351</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="B36" s="5">
         <v>1</v>
@@ -6210,12 +6926,15 @@
         <v>4</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+        <v>408</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="B37" s="5">
         <v>1</v>
@@ -6227,12 +6946,15 @@
         <v>4</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+        <v>410</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="B38" s="5">
         <v>1</v>
@@ -6244,10 +6966,13 @@
         <v>4</v>
       </c>
       <c r="E38" s="5"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F38" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="B39" s="5">
         <v>1</v>
@@ -6259,10 +6984,13 @@
         <v>4</v>
       </c>
       <c r="E39" s="5"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F39" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="B40" s="5">
         <v>1</v>
@@ -6274,12 +7002,15 @@
         <v>4</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+        <v>437</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="B41" s="5">
         <v>1</v>
@@ -6291,155 +7022,185 @@
         <v>4</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="B42" s="5">
         <v>1</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="D42" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="B43" s="5">
         <v>1</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="D43" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+        <v>445</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="B44" s="5">
         <v>1</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="D44" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E44" s="5"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F44" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="B45" s="5">
         <v>1</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="D45" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>391</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+        <v>381</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="B46" s="5">
         <v>1</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="D46" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E46" s="5"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F46" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="B47" s="5">
         <v>1</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="D47" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E47" s="5"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F47" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="B48" s="5">
         <v>1</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="D48" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+        <v>386</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="B49" s="5">
         <v>1</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="D49" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+        <v>401</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="B50" s="5">
         <v>1</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="D50" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E50" s="5"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F50" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
         <v>22</v>
       </c>
@@ -6453,10 +7214,13 @@
         <v>2</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+        <v>188</v>
+      </c>
+      <c r="F51" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>23</v>
       </c>
@@ -6470,8 +7234,11 @@
         <v>2</v>
       </c>
       <c r="E52" s="5"/>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F52" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
         <v>27</v>
       </c>
@@ -6485,8 +7252,11 @@
         <v>2</v>
       </c>
       <c r="E53" s="5"/>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F53" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
         <v>26</v>
       </c>
@@ -6500,8 +7270,11 @@
         <v>2</v>
       </c>
       <c r="E54" s="5"/>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F54" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
         <v>28</v>
       </c>
@@ -6515,8 +7288,11 @@
         <v>2</v>
       </c>
       <c r="E55" s="5"/>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F55" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
         <v>30</v>
       </c>
@@ -6530,8 +7306,11 @@
         <v>2</v>
       </c>
       <c r="E56" s="5"/>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F56" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
         <v>52</v>
       </c>
@@ -6545,10 +7324,13 @@
         <v>2</v>
       </c>
       <c r="E57" s="5"/>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F57" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="B58" s="5">
         <v>1</v>
@@ -6560,10 +7342,13 @@
         <v>2</v>
       </c>
       <c r="E58" s="5"/>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F58" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="B59" s="5">
         <v>1</v>
@@ -6575,12 +7360,15 @@
         <v>2</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+        <v>529</v>
+      </c>
+      <c r="F59" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="B60" s="5">
         <v>1</v>
@@ -6592,12 +7380,15 @@
         <v>2</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+        <v>371</v>
+      </c>
+      <c r="F60" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="B61" s="5">
         <v>1</v>
@@ -6609,12 +7400,15 @@
         <v>2</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+        <v>375</v>
+      </c>
+      <c r="F61" s="10" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="B62" s="5">
         <v>1</v>
@@ -6626,12 +7420,15 @@
         <v>2</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+        <v>377</v>
+      </c>
+      <c r="F62" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="B63" s="5">
         <v>1</v>
@@ -6643,10 +7440,13 @@
         <v>2</v>
       </c>
       <c r="E63" s="5"/>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F63" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="B64" s="5">
         <v>1</v>
@@ -6658,12 +7458,15 @@
         <v>2</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+        <v>340</v>
+      </c>
+      <c r="F64" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="B65" s="5">
         <v>1</v>
@@ -6675,12 +7478,15 @@
         <v>2</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+        <v>341</v>
+      </c>
+      <c r="F65" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="B66" s="5">
         <v>1</v>
@@ -6692,12 +7498,15 @@
         <v>2</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+        <v>412</v>
+      </c>
+      <c r="F66" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="B67" s="5">
         <v>1</v>
@@ -6709,12 +7518,15 @@
         <v>2</v>
       </c>
       <c r="E67" s="7" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+        <v>414</v>
+      </c>
+      <c r="F67" s="11" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="B68" s="5">
         <v>1</v>
@@ -6726,12 +7538,15 @@
         <v>2</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+        <v>416</v>
+      </c>
+      <c r="F68" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="B69" s="5">
         <v>1</v>
@@ -6743,10 +7558,13 @@
         <v>2</v>
       </c>
       <c r="E69" s="5"/>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F69" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="B70" s="5">
         <v>1</v>
@@ -6758,12 +7576,15 @@
         <v>2</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+        <v>420</v>
+      </c>
+      <c r="F70" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="B71" s="5">
         <v>1</v>
@@ -6775,12 +7596,15 @@
         <v>2</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+        <v>428</v>
+      </c>
+      <c r="F71" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="B72" s="5">
         <v>1</v>
@@ -6792,12 +7616,15 @@
         <v>2</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+        <v>399</v>
+      </c>
+      <c r="F72" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="B73" s="5">
         <v>1</v>
@@ -6809,12 +7636,15 @@
         <v>2</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+        <v>275</v>
+      </c>
+      <c r="F73" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="B74" s="5">
         <v>1</v>
@@ -6826,10 +7656,13 @@
         <v>2</v>
       </c>
       <c r="E74" s="5"/>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F74" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="B75" s="5">
         <v>1</v>
@@ -6841,25 +7674,58 @@
         <v>2</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+        <v>440</v>
+      </c>
+      <c r="F75" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="B76" s="5">
         <v>1</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="D76" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>409</v>
-      </c>
+        <v>399</v>
+      </c>
+      <c r="F76" s="10" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F77" s="10"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F78" s="10"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F79" s="10"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F80" s="10"/>
+    </row>
+    <row r="81" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F81" s="10"/>
+    </row>
+    <row r="82" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F82" s="10"/>
+    </row>
+    <row r="83" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F83" s="10"/>
+    </row>
+    <row r="84" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F84" s="10"/>
+    </row>
+    <row r="85" spans="6:6" x14ac:dyDescent="0.25">
+      <c r="F85" s="10"/>
     </row>
   </sheetData>
   <hyperlinks>
@@ -6949,7 +7815,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF74C291-3FDB-4574-B9CC-3F7D5D446E44}">
-  <dimension ref="A1:E31"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="56.42578125" customWidth="1"/>
@@ -6959,7 +7825,7 @@
     <col min="5" max="5" width="16.5703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>73</v>
       </c>
@@ -6967,7 +7833,7 @@
         <v>72</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>74</v>
@@ -6975,496 +7841,589 @@
       <c r="E1" s="9" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="9" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="B2" s="5">
+        <v>1</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="5" t="s">
+        <v>476</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="B3" s="5">
+        <v>1</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>478</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="B4" s="5">
+        <v>1</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>479</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="B5" s="5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>481</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="B6" s="5">
+        <v>1</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>483</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="B7" s="5">
+        <v>1</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="B2" s="5">
-        <v>1</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E2" s="5" t="s">
+      <c r="F7" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>486</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="B8" s="5">
+        <v>1</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="5" t="s">
         <v>487</v>
       </c>
-      <c r="B3" s="5">
-        <v>1</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" s="5" t="s">
+      <c r="F8" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
         <v>488</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="B9" s="5">
+        <v>1</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>489</v>
       </c>
-      <c r="B4" s="5">
-        <v>1</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="5" t="s">
+      <c r="F9" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B10" s="5">
+        <v>1</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>316</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="B11" s="5">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="B12" s="5">
+        <v>1</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B13" s="5">
+        <v>1</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>323</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B14" s="5">
+        <v>1</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>325</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="B15" s="5">
+        <v>1</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>490</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+      <c r="B16" s="5">
+        <v>1</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>491</v>
       </c>
-      <c r="B5" s="5">
-        <v>1</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="F16" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="B17" s="5">
+        <v>1</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="B18" s="5">
+        <v>1</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="B19" s="5">
+        <v>1</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>501</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="B20" s="5">
+        <v>1</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="B21" s="5">
+        <v>1</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>468</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="B22" s="5">
+        <v>1</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="B23" s="5">
+        <v>1</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="B24" s="5">
+        <v>1</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="B25" s="5">
+        <v>1</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>473</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="B26" s="5">
+        <v>1</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>403</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>492</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="B6" s="5">
-        <v>1</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
+      <c r="B27" s="5">
+        <v>1</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="B7" s="5">
-        <v>1</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="5" t="s">
+      <c r="B28" s="5">
+        <v>1</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
         <v>496</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
+      <c r="B29" s="5">
+        <v>1</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="B8" s="5">
-        <v>1</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="5" t="s">
+      <c r="B30" s="5">
+        <v>1</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>317</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E30" s="5" t="s">
         <v>498</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="B9" s="5">
-        <v>1</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="B10" s="5">
-        <v>1</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="B11" s="5">
-        <v>1</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="B12" s="5">
-        <v>1</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="B13" s="5">
-        <v>1</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="B14" s="5">
-        <v>1</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="B15" s="5">
-        <v>1</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="B16" s="5">
-        <v>1</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E16" s="5" t="s">
+      <c r="F30" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
         <v>502</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="B17" s="5">
-        <v>1</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="B18" s="5">
-        <v>1</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>511</v>
-      </c>
-      <c r="B19" s="5">
-        <v>1</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="B20" s="5">
-        <v>1</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="B21" s="5">
-        <v>1</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="B22" s="5">
-        <v>1</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E22" s="5"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="B23" s="5">
-        <v>1</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E23" s="5"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="B24" s="5">
-        <v>1</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E24" s="5"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="B25" s="5">
-        <v>1</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="B26" s="5">
-        <v>1</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>413</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E26" s="5"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>503</v>
-      </c>
-      <c r="B27" s="5">
-        <v>1</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E27" s="5"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="B28" s="5">
-        <v>1</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E28" s="5"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="B29" s="5">
-        <v>1</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E29" s="5"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="B30" s="5">
-        <v>1</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>513</v>
-      </c>
       <c r="B31" s="5">
         <v>1</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E31" s="5"/>
+      <c r="F31" s="5" t="s">
+        <v>533</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
@@ -7509,7 +8468,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA307CC6-0015-40D6-AA89-BC43524855C1}">
-  <dimension ref="A1:E103"/>
+  <dimension ref="A1:F103"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="61.85546875" customWidth="1"/>
@@ -7518,7 +8477,7 @@
     <col min="5" max="5" width="18.5703125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="8" t="s">
         <v>73</v>
       </c>
@@ -7526,7 +8485,7 @@
         <v>72</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="D1" s="9" t="s">
         <v>74</v>
@@ -7534,42 +8493,51 @@
       <c r="E1" s="9" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="9" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>91</v>
+        <v>536</v>
       </c>
       <c r="B2" s="5">
         <v>1</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="D2" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>99</v>
+        <v>537</v>
       </c>
       <c r="B3" s="5">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="D3" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>71</v>
       </c>
@@ -7577,7 +8545,7 @@
         <v>1</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>4</v>
@@ -7585,8 +8553,11 @@
       <c r="E4" s="5" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>77</v>
       </c>
@@ -7594,16 +8565,19 @@
         <v>1</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>78</v>
       </c>
@@ -7611,501 +8585,591 @@
         <v>1</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E6" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="B7" s="5">
+        <v>1</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="B8" s="5">
+        <v>1</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="B9" s="5">
+        <v>1</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="B10" s="5">
+        <v>1</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B7" s="5">
-        <v>1</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B8" s="5">
-        <v>1</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+      <c r="F10" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="B11" s="5">
+        <v>1</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E11" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="B9" s="5">
-        <v>1</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B10" s="5">
-        <v>1</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="5" t="s">
+      <c r="F11" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="B12" s="5">
+        <v>1</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+      <c r="F12" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="B13" s="5">
+        <v>1</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="B11" s="5">
-        <v>1</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E11" s="5" t="s">
+      <c r="F13" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="B14" s="5">
+        <v>1</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+      <c r="F14" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B15" s="5">
+        <v>1</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B12" s="5">
-        <v>1</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E12" s="5" t="s">
+      <c r="B16" s="5">
+        <v>1</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E16" s="5" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+      <c r="F16" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B13" s="5">
-        <v>1</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E13" s="5" t="s">
+      <c r="B17" s="5">
+        <v>1</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E17" s="5" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
+      <c r="F17" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="B14" s="5">
-        <v>1</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E14" s="5" t="s">
+      <c r="B18" s="5">
+        <v>1</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E18" s="5" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="B15" s="5">
-        <v>1</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B16" s="5">
-        <v>1</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B17" s="5">
-        <v>1</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B18" s="5">
-        <v>1</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="B19" s="5">
         <v>1</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="D19" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>100</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B20" s="5">
+        <v>1</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="B21" s="5">
+        <v>1</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B22" s="5">
+        <v>1</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B23" s="5">
+        <v>1</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B24" s="5">
+        <v>1</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="B20" s="5">
-        <v>1</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E20" s="5" t="s">
+      <c r="F24" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="B25" s="5">
+        <v>1</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E25" s="5" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+      <c r="F25" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="B21" s="5">
-        <v>1</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E21" s="5" t="s">
+      <c r="B26" s="5">
+        <v>1</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E26" s="5" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="F26" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B22" s="5">
-        <v>1</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E22" s="5" t="s">
+      <c r="B27" s="5">
+        <v>1</v>
+      </c>
+      <c r="C27" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E27" s="5" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
+      <c r="F27" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B23" s="5">
-        <v>1</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E23" s="5" t="s">
+      <c r="B28" s="5">
+        <v>1</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>503</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E28" s="5" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="B24" s="5">
-        <v>1</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B25" s="5">
-        <v>1</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="B26" s="5">
-        <v>1</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B27" s="5">
-        <v>1</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="B28" s="5">
-        <v>1</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>514</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F28" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="B29" s="5">
         <v>1</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="D29" s="5" t="s">
         <v>4</v>
       </c>
       <c r="E29" s="5"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F29" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="B30" s="5">
         <v>1</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="D30" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>515</v>
+        <v>504</v>
       </c>
       <c r="B31" s="5">
         <v>1</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>517</v>
+        <v>506</v>
       </c>
       <c r="D31" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+        <v>505</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="B32" s="5">
         <v>1</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>519</v>
+        <v>508</v>
       </c>
       <c r="D32" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E32" s="5"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F32" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="B33" s="5">
         <v>1</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="D33" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E33" s="5"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F33" s="5" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="B34" s="5">
         <v>1</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>514</v>
+        <v>503</v>
       </c>
       <c r="D34" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E34" s="5"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F34" s="5" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="B35" s="5">
         <v>1</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>518</v>
+        <v>507</v>
       </c>
       <c r="D35" s="5" t="s">
         <v>2</v>
       </c>
       <c r="E35" s="5"/>
+      <c r="F35" s="5" t="s">
+        <v>533</v>
+      </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="B103" s="1">
         <f>SUM(B2:B101)</f>
